--- a/data/trans_orig/P16A10-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A10-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27299</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51703</t>
+          <t>52235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25284</t>
+          <t>25437</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47632</t>
+          <t>48684</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59058</t>
+          <t>59473</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91403</t>
+          <t>92866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>641291</t>
+          <t>640759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665695</t>
+          <t>665041</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>640719</t>
+          <t>639667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663067</t>
+          <t>662914</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1289942</t>
+          <t>1288479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1322287</t>
+          <t>1321872</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43865</t>
+          <t>44970</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74806</t>
+          <t>74560</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39452</t>
+          <t>39065</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68589</t>
+          <t>68630</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91668</t>
+          <t>90384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133173</t>
+          <t>131247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>886994</t>
+          <t>887240</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>917935</t>
+          <t>916830</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>899804</t>
+          <t>899763</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>928941</t>
+          <t>929328</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1797020</t>
+          <t>1798946</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1838525</t>
+          <t>1839809</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26499</t>
+          <t>26468</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48446</t>
+          <t>50068</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23594</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48215</t>
+          <t>46519</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56531</t>
+          <t>55269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88495</t>
+          <t>89573</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>630063</t>
+          <t>628441</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652010</t>
+          <t>652041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635626</t>
+          <t>637322</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660247</t>
+          <t>660028</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1273855</t>
+          <t>1272777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1305819</t>
+          <t>1307081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33677</t>
+          <t>32649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58339</t>
+          <t>57676</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44143</t>
+          <t>44074</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74772</t>
+          <t>74575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84992</t>
+          <t>83469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123538</t>
+          <t>119903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>883883</t>
+          <t>884546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>908545</t>
+          <t>909573</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>963840</t>
+          <t>964037</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>994469</t>
+          <t>994538</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857296</t>
+          <t>1860931</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1895842</t>
+          <t>1897365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151478</t>
+          <t>153538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205422</t>
+          <t>202598</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154492</t>
+          <t>154493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204222</t>
+          <t>207824</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>319374</t>
+          <t>322063</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>391562</t>
+          <t>393925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3070103</t>
+          <t>3072927</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3124047</t>
+          <t>3121987</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3174975</t>
+          <t>3171373</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3224705</t>
+          <t>3224704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6263160</t>
+          <t>6260797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6335348</t>
+          <t>6332659</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>21930</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46683</t>
+          <t>46057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28941</t>
+          <t>28817</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53062</t>
+          <t>54120</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57400</t>
+          <t>57231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92132</t>
+          <t>93260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>654896</t>
+          <t>655522</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>678350</t>
+          <t>679649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>642945</t>
+          <t>641887</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>667066</t>
+          <t>667190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1305453</t>
+          <t>1304325</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1340185</t>
+          <t>1340354</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36126</t>
+          <t>36755</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67349</t>
+          <t>65231</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36756</t>
+          <t>36831</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66932</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81549</t>
+          <t>80790</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124961</t>
+          <t>121573</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>950598</t>
+          <t>952716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>981821</t>
+          <t>981192</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>962026</t>
+          <t>963756</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>992202</t>
+          <t>992127</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1921944</t>
+          <t>1925332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1965356</t>
+          <t>1966115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25404</t>
+          <t>24790</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51343</t>
+          <t>51045</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18683</t>
+          <t>18614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40980</t>
+          <t>40802</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50426</t>
+          <t>49975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82924</t>
+          <t>81505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>705195</t>
+          <t>705493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>731134</t>
+          <t>731748</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>734308</t>
+          <t>734486</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>756605</t>
+          <t>756674</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1448902</t>
+          <t>1450321</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1481400</t>
+          <t>1481851</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47910</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81219</t>
+          <t>77961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38163</t>
+          <t>39709</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68507</t>
+          <t>69560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92044</t>
+          <t>93772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135416</t>
+          <t>136330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>862720</t>
+          <t>865978</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>896029</t>
+          <t>897593</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>980410</t>
+          <t>979357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1010754</t>
+          <t>1009208</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857440</t>
+          <t>1856526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1900812</t>
+          <t>1899084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153180</t>
+          <t>155255</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>207758</t>
+          <t>211198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,82 +4067,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>170460</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>146419</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>199323</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>350949</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>312413</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>388024</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>4,48%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>170460</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>144719</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>196865</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>350949</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>314112</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>386473</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3212245</t>
+          <t>3208805</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3266823</t>
+          <t>3264748</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,82 +4180,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>95,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3378710</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3349847</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3402751</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>94,38%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6167</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6618224</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6581149</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6656760</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>95,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3378710</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3352305</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3404451</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,2%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6167</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6618224</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6582700</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6655061</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>94,96%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32605</t>
+          <t>31817</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58310</t>
+          <t>57765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33772</t>
+          <t>34105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61096</t>
+          <t>62079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71948</t>
+          <t>71110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108768</t>
+          <t>110260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>616490</t>
+          <t>617035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>642195</t>
+          <t>642983</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>611743</t>
+          <t>610760</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>639067</t>
+          <t>638734</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1238871</t>
+          <t>1237379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1275691</t>
+          <t>1276529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44333</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74148</t>
+          <t>74369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,82 +4985,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>53127</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>38453</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>69653</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>111547</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>89719</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>133345</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>4,34%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>53127</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>39080</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>71155</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>111547</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>92540</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>134137</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>948283</t>
+          <t>948062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>978098</t>
+          <t>978211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,82 +5098,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>95,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>989786</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>973260</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1004460</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>94,91%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1953797</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1931999</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1975625</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>94,6%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>93,54%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>95,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>989786</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>971758</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1003833</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,91%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,18%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>96,25%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1953797</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1931207</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1972804</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>94,6%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>93,51%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35620</t>
+          <t>35783</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62032</t>
+          <t>62988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31587</t>
+          <t>32943</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59701</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72999</t>
+          <t>73199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113150</t>
+          <t>112596</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>697520</t>
+          <t>696564</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>723932</t>
+          <t>723769</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>725310</t>
+          <t>725147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>753424</t>
+          <t>752068</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1431413</t>
+          <t>1431967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1471564</t>
+          <t>1471364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40818</t>
+          <t>40754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68865</t>
+          <t>68453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33610</t>
+          <t>33135</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63446</t>
+          <t>64345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85354</t>
+          <t>83627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126533</t>
+          <t>124990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>868702</t>
+          <t>869114</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>896749</t>
+          <t>896813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>980333</t>
+          <t>979434</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1010169</t>
+          <t>1010644</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1854813</t>
+          <t>1856356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1895992</t>
+          <t>1897719</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>173541</t>
+          <t>174520</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>230261</t>
+          <t>230470</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163842</t>
+          <t>163587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>219186</t>
+          <t>222624</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>353330</t>
+          <t>357015</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>434981</t>
+          <t>434160</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3164089</t>
+          <t>3163880</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3220809</t>
+          <t>3219830</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3325356</t>
+          <t>3321918</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3380700</t>
+          <t>3380955</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6503911</t>
+          <t>6504732</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6585562</t>
+          <t>6581877</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32385</t>
+          <t>32891</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53170</t>
+          <t>54831</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38002</t>
+          <t>37765</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57505</t>
+          <t>58537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75964</t>
+          <t>75876</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105879</t>
+          <t>105856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>582271</t>
+          <t>580610</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>603056</t>
+          <t>602550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>618247</t>
+          <t>617215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>637750</t>
+          <t>637987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1205315</t>
+          <t>1205338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1235230</t>
+          <t>1235318</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>18500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54858</t>
+          <t>54506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37295</t>
+          <t>36572</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56616</t>
+          <t>56381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,47 +6967,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>83889</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>58106</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>102373</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>3,9%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>83889</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>58650</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>101543</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1138006</t>
+          <t>1138358</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1171652</t>
+          <t>1174364</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>900879</t>
+          <t>901114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>920200</t>
+          <t>920923</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,47 +7080,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2335</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2066470</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2047986</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2092253</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>96,1%</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2335</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2066470</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>2048816</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2091709</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,1%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35173</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59983</t>
+          <t>59490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15275</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43348</t>
+          <t>42835</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51146</t>
+          <t>50142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98516</t>
+          <t>96240</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643701</t>
+          <t>644194</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668511</t>
+          <t>669356</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>889452</t>
+          <t>889965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>917525</t>
+          <t>918427</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1537968</t>
+          <t>1540244</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1585338</t>
+          <t>1586342</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47578</t>
+          <t>47847</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73091</t>
+          <t>73207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44118</t>
+          <t>44062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70046</t>
+          <t>70032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97444</t>
+          <t>98321</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132928</t>
+          <t>132983</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853740</t>
+          <t>853624</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879253</t>
+          <t>878984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1021328</t>
+          <t>1021342</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1047256</t>
+          <t>1047312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885277</t>
+          <t>1885222</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1920761</t>
+          <t>1919884</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141855</t>
+          <t>135483</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>213766</t>
+          <t>213993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>144087</t>
+          <t>146292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>202394</t>
+          <t>203907</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>317171</t>
+          <t>320204</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>406526</t>
+          <t>408796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3245054</t>
+          <t>3244827</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3316965</t>
+          <t>3323337</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3455027</t>
+          <t>3453514</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3513334</t>
+          <t>3511129</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6709715</t>
+          <t>6707445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6799070</t>
+          <t>6796037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A10-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A10-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27953</t>
+          <t>28340</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52235</t>
+          <t>51744</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25437</t>
+          <t>25746</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48684</t>
+          <t>50412</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59473</t>
+          <t>60492</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92866</t>
+          <t>92957</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>640759</t>
+          <t>641250</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665041</t>
+          <t>664654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>639667</t>
+          <t>637939</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>662914</t>
+          <t>662605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1288479</t>
+          <t>1288388</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1321872</t>
+          <t>1320853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>44000</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74560</t>
+          <t>74072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>38614</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68630</t>
+          <t>68221</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90384</t>
+          <t>90934</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131247</t>
+          <t>131390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>887240</t>
+          <t>887728</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>916830</t>
+          <t>917800</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>899763</t>
+          <t>900172</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>929328</t>
+          <t>929779</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1798946</t>
+          <t>1798803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1839809</t>
+          <t>1839259</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26468</t>
+          <t>25633</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50068</t>
+          <t>48938</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23813</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46519</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55269</t>
+          <t>54954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89573</t>
+          <t>87921</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628441</t>
+          <t>629571</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652041</t>
+          <t>652876</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637322</t>
+          <t>637110</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660028</t>
+          <t>659917</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1272777</t>
+          <t>1274429</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1307081</t>
+          <t>1307396</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32649</t>
+          <t>33080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57676</t>
+          <t>56460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44074</t>
+          <t>43364</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74575</t>
+          <t>72933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83469</t>
+          <t>83170</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119903</t>
+          <t>121433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>884546</t>
+          <t>885762</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>909573</t>
+          <t>909142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>964037</t>
+          <t>965679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>994538</t>
+          <t>995248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1860931</t>
+          <t>1859401</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897365</t>
+          <t>1897664</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153538</t>
+          <t>153862</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>202598</t>
+          <t>202443</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154493</t>
+          <t>155486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207824</t>
+          <t>205837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>322063</t>
+          <t>319303</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>393925</t>
+          <t>393067</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3072927</t>
+          <t>3073082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3121987</t>
+          <t>3121663</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3171373</t>
+          <t>3173360</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3224704</t>
+          <t>3223711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6260797</t>
+          <t>6261655</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6332659</t>
+          <t>6335419</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21930</t>
+          <t>23729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46057</t>
+          <t>46670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28817</t>
+          <t>27073</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54120</t>
+          <t>52117</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57231</t>
+          <t>58221</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93260</t>
+          <t>92066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>655522</t>
+          <t>654909</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>679649</t>
+          <t>677850</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641887</t>
+          <t>643890</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>667190</t>
+          <t>668934</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1304325</t>
+          <t>1305519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1340354</t>
+          <t>1339364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>37507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65231</t>
+          <t>66753</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36831</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65202</t>
+          <t>64808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80790</t>
+          <t>79675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121573</t>
+          <t>120658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>952716</t>
+          <t>951194</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>981192</t>
+          <t>980440</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>963756</t>
+          <t>964150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>992127</t>
+          <t>992738</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1925332</t>
+          <t>1926247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1966115</t>
+          <t>1967230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24790</t>
+          <t>25523</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51045</t>
+          <t>50799</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40802</t>
+          <t>39355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49975</t>
+          <t>46848</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81505</t>
+          <t>83185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>705493</t>
+          <t>705739</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>731748</t>
+          <t>731015</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>734486</t>
+          <t>735933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>756674</t>
+          <t>756898</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1450321</t>
+          <t>1448641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1481851</t>
+          <t>1484978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46346</t>
+          <t>46781</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77961</t>
+          <t>78877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39709</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69560</t>
+          <t>69418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93772</t>
+          <t>94687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136330</t>
+          <t>137975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>865978</t>
+          <t>865062</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>897593</t>
+          <t>897158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>979357</t>
+          <t>979499</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1009208</t>
+          <t>1009009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1856526</t>
+          <t>1854881</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1899084</t>
+          <t>1898169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155255</t>
+          <t>154266</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>211198</t>
+          <t>214229</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>146419</t>
+          <t>145695</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>199323</t>
+          <t>196463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>312413</t>
+          <t>314378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>388024</t>
+          <t>386052</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3208805</t>
+          <t>3205774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3264748</t>
+          <t>3265737</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3349847</t>
+          <t>3352707</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3402751</t>
+          <t>3403475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6581149</t>
+          <t>6583121</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6656760</t>
+          <t>6654795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31817</t>
+          <t>32729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57765</t>
+          <t>57158</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34105</t>
+          <t>33013</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62079</t>
+          <t>60892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71110</t>
+          <t>70594</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110260</t>
+          <t>107367</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>617035</t>
+          <t>617642</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>642983</t>
+          <t>642071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>610760</t>
+          <t>611947</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>638734</t>
+          <t>639826</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1237379</t>
+          <t>1240272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1276529</t>
+          <t>1277045</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>45105</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74369</t>
+          <t>74833</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38453</t>
+          <t>39374</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69653</t>
+          <t>70728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89719</t>
+          <t>91243</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133345</t>
+          <t>133816</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>948062</t>
+          <t>947598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>978211</t>
+          <t>977326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>973260</t>
+          <t>972185</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1004460</t>
+          <t>1003539</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1931999</t>
+          <t>1931528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1975625</t>
+          <t>1974101</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35783</t>
+          <t>36007</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62988</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32943</t>
+          <t>31905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59864</t>
+          <t>60081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73199</t>
+          <t>73598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112596</t>
+          <t>111305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>696564</t>
+          <t>697521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>723769</t>
+          <t>723545</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>725147</t>
+          <t>724930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>752068</t>
+          <t>753106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1431967</t>
+          <t>1433258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1471364</t>
+          <t>1470965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40754</t>
+          <t>41229</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68453</t>
+          <t>68820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33135</t>
+          <t>33892</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64345</t>
+          <t>64213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83627</t>
+          <t>82978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124990</t>
+          <t>124435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>869114</t>
+          <t>868747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>896813</t>
+          <t>896338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>979434</t>
+          <t>979566</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1010644</t>
+          <t>1009887</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1856356</t>
+          <t>1856911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897719</t>
+          <t>1898368</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174520</t>
+          <t>176028</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>230470</t>
+          <t>232086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163587</t>
+          <t>163437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>222624</t>
+          <t>222554</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>357015</t>
+          <t>358205</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>434160</t>
+          <t>438331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3163880</t>
+          <t>3162264</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3219830</t>
+          <t>3218322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3321918</t>
+          <t>3321988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3380955</t>
+          <t>3381105</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6504732</t>
+          <t>6500561</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6581877</t>
+          <t>6580687</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42497</t>
+          <t>47065</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32891</t>
+          <t>36682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54831</t>
+          <t>60748</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>46957</t>
+          <t>50729</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37765</t>
+          <t>41073</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58537</t>
+          <t>63071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>89454</t>
+          <t>97794</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75876</t>
+          <t>83423</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105856</t>
+          <t>116773</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>592944</t>
+          <t>643645</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>580610</t>
+          <t>629962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>602550</t>
+          <t>654028</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>628795</t>
+          <t>682384</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>617215</t>
+          <t>670042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>637987</t>
+          <t>692040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1221740</t>
+          <t>1326029</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1205338</t>
+          <t>1307050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1235318</t>
+          <t>1340400</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38444</t>
+          <t>42773</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>32207</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54506</t>
+          <t>54514</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45445</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36572</t>
+          <t>39879</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56381</t>
+          <t>61687</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>83889</t>
+          <t>92689</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58106</t>
+          <t>77374</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102373</t>
+          <t>109092</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1154420</t>
+          <t>1006144</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1138358</t>
+          <t>994403</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1174364</t>
+          <t>1016710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>912050</t>
+          <t>1020210</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>901114</t>
+          <t>1008439</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>920923</t>
+          <t>1030247</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2066470</t>
+          <t>2026354</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2047986</t>
+          <t>2009951</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2092253</t>
+          <t>2041669</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957495</t>
+          <t>1070126</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957495</t>
+          <t>1070126</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957495</t>
+          <t>1070126</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150359</t>
+          <t>2119043</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150359</t>
+          <t>2119043</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150359</t>
+          <t>2119043</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>46532</t>
+          <t>51204</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34328</t>
+          <t>38988</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59490</t>
+          <t>66119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30390</t>
+          <t>35407</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>26779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42835</t>
+          <t>45818</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>76923</t>
+          <t>86611</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50142</t>
+          <t>72224</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96240</t>
+          <t>105703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>657152</t>
+          <t>750882</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644194</t>
+          <t>735967</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669356</t>
+          <t>763098</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>902410</t>
+          <t>776256</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>889965</t>
+          <t>765845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>918427</t>
+          <t>784884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1559561</t>
+          <t>1527137</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1540244</t>
+          <t>1508045</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1586342</t>
+          <t>1541524</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>59080</t>
+          <t>63191</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47847</t>
+          <t>49749</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73207</t>
+          <t>76475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56738</t>
+          <t>62794</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44062</t>
+          <t>52122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70032</t>
+          <t>74869</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>115818</t>
+          <t>125985</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98321</t>
+          <t>108544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132983</t>
+          <t>144292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>867751</t>
+          <t>926871</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853624</t>
+          <t>913587</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>878984</t>
+          <t>940313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1034636</t>
+          <t>1054237</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1021342</t>
+          <t>1042162</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1047312</t>
+          <t>1064909</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1902387</t>
+          <t>1981108</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885222</t>
+          <t>1962801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1919884</t>
+          <t>1998549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>186554</t>
+          <t>204233</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>135483</t>
+          <t>180299</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>213993</t>
+          <t>230228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>179530</t>
+          <t>198846</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>146292</t>
+          <t>179190</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>203907</t>
+          <t>222350</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>366084</t>
+          <t>403079</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>320204</t>
+          <t>370759</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>408796</t>
+          <t>439152</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3272266</t>
+          <t>3327542</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3244827</t>
+          <t>3301547</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3323337</t>
+          <t>3351476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3477891</t>
+          <t>3533087</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3453514</t>
+          <t>3509583</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3511129</t>
+          <t>3552743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6750157</t>
+          <t>6860628</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6707445</t>
+          <t>6824555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6796037</t>
+          <t>6892948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657421</t>
+          <t>3731933</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657421</t>
+          <t>3731933</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657421</t>
+          <t>3731933</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7116241</t>
+          <t>7263707</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7116241</t>
+          <t>7263707</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7116241</t>
+          <t>7263707</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
